--- a/artfynd/A 53658-2025 artfynd.xlsx
+++ b/artfynd/A 53658-2025 artfynd.xlsx
@@ -10501,7 +10501,7 @@
         <v>127290144</v>
       </c>
       <c r="B94" t="n">
-        <v>78788</v>
+        <v>78770</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10595,10 +10595,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>127297096</v>
+        <v>127289839</v>
       </c>
       <c r="B95" t="n">
-        <v>79029</v>
+        <v>79600</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10606,21 +10606,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>229821</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10630,10 +10630,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>475097</v>
+        <v>475045</v>
       </c>
       <c r="R95" t="n">
-        <v>6831146</v>
+        <v>6831117</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10692,10 +10692,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>127289839</v>
+        <v>127297096</v>
       </c>
       <c r="B96" t="n">
-        <v>79618</v>
+        <v>79011</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10703,21 +10703,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>229821</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10727,10 +10727,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>475045</v>
+        <v>475097</v>
       </c>
       <c r="R96" t="n">
-        <v>6831117</v>
+        <v>6831146</v>
       </c>
       <c r="S96" t="n">
         <v>15</v>
@@ -10792,7 +10792,7 @@
         <v>127289948</v>
       </c>
       <c r="B97" t="n">
-        <v>57832</v>
+        <v>57817</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10889,7 +10889,7 @@
         <v>127296988</v>
       </c>
       <c r="B98" t="n">
-        <v>78788</v>
+        <v>78770</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10986,7 +10986,7 @@
         <v>127289924</v>
       </c>
       <c r="B99" t="n">
-        <v>78788</v>
+        <v>78770</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
